--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0002T0006Z000C1N30_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0002T0006Z000C1N30_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>5.70087712549569</v>
+        <v>0.9263925328930496</v>
       </c>
       <c r="D2" t="n">
-        <v>5.610855699258053</v>
+        <v>0.9117640511294337</v>
       </c>
       <c r="E2" t="n">
-        <v>14.59079743453946</v>
+        <v>2.371004583112661</v>
       </c>
       <c r="F2" t="n">
-        <v>14.74185494794291</v>
+        <v>2.395551429040722</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.9285229378822</v>
+        <v>4.375884977405858</v>
       </c>
       <c r="D3" t="n">
-        <v>26.85874821274358</v>
+        <v>4.364546584570832</v>
       </c>
       <c r="E3" t="n">
-        <v>14.59079743453946</v>
+        <v>2.371004583112661</v>
       </c>
       <c r="F3" t="n">
-        <v>14.74185494794291</v>
+        <v>2.395551429040722</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.77016795951301</v>
+        <v>5.325152293420865</v>
       </c>
       <c r="D4" t="n">
-        <v>32.63350103308717</v>
+        <v>5.302943917876665</v>
       </c>
       <c r="E4" t="n">
-        <v>14.59079743453946</v>
+        <v>2.371004583112661</v>
       </c>
       <c r="F4" t="n">
-        <v>14.74185494794291</v>
+        <v>2.395551429040722</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>46.17846382274986</v>
+        <v>7.504000371196852</v>
       </c>
       <c r="D5" t="n">
-        <v>46.58140100647481</v>
+        <v>7.569477663552157</v>
       </c>
       <c r="E5" t="n">
-        <v>14.59079743453946</v>
+        <v>2.371004583112661</v>
       </c>
       <c r="F5" t="n">
-        <v>14.74185494794291</v>
+        <v>2.395551429040722</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
